--- a/OneDrive - SENAC - SP/UC6_Algoritmo/Aula12/portal_alunos.xlsx
+++ b/OneDrive - SENAC - SP/UC6_Algoritmo/Aula12/portal_alunos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,17 @@
           <t>altura</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Lipao</t>
+        </is>
+      </c>
+      <c r="E1" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,6 +455,29 @@
       </c>
       <c r="C2" t="n">
         <v>1.78</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lipao</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
